--- a/matematicas_1ESOA/notas/E1A_evalfinal.xlsx
+++ b/matematicas_1ESOA/notas/E1A_evalfinal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ac4744725179635e/Desktop/sapere_aude/matematicas_1ESOA/notas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="14_{20891835-A900-4E6F-B467-720F2D4F79E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4E1D4FB-D7A0-46CB-B835-FC153039D3C5}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="14_{4378DAE7-DBE3-4408-84D4-85DD99A0A7A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85D10536-EA85-4838-91C4-099A8A27A35D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -705,28 +705,7 @@
     <cellStyle name="Normal 2" xfId="3" xr:uid="{11178035-4857-4F54-A6C2-705F42B4A1BB}"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF808080"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <fill>
         <patternFill>
@@ -1004,6 +983,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2446,7 +2429,7 @@
         <v>5</v>
       </c>
       <c r="E14" s="31">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F14" s="31">
         <v>6</v>
@@ -2486,7 +2469,7 @@
       </c>
       <c r="R14" s="13">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S14" s="14" t="str">
         <f t="shared" si="1"/>
@@ -2498,7 +2481,7 @@
       </c>
       <c r="U14" s="15">
         <f t="shared" si="3"/>
-        <v>5.7777777777777777</v>
+        <v>5.666666666666667</v>
       </c>
       <c r="W14" s="33"/>
       <c r="X14" s="33"/>
@@ -3351,7 +3334,7 @@
       </c>
       <c r="E27" s="26">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F27" s="26">
         <f t="shared" si="4"/>
@@ -3403,7 +3386,7 @@
       </c>
       <c r="R27" s="27">
         <f>AVERAGE(R2:R26)</f>
-        <v>1.1599999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="S27" s="14" t="str">
         <f>IF(T27&lt;$T$27,"X","")</f>
@@ -3415,7 +3398,7 @@
       </c>
       <c r="U27" s="15">
         <f>(SUM(C2:Q26)+(COUNTIF(C2:Q26,"10-M")*10))/(COUNTIF(C2:Q26,"10-M")+COUNT(C2:Q26)+COUNTIF(C2:Q26,"NP")+COUNTIF(C2:Q26,"NE"))</f>
-        <v>6.6036036036036032</v>
+        <v>6.5990990990990994</v>
       </c>
     </row>
     <row r="28" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
@@ -3432,7 +3415,7 @@
       </c>
       <c r="E28" s="29">
         <f t="shared" si="5"/>
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="F28" s="29">
         <f t="shared" si="5"/>
@@ -3492,15 +3475,15 @@
     <mergeCell ref="W15:Y15"/>
   </mergeCells>
   <conditionalFormatting sqref="C2:Q26">
-    <cfRule type="cellIs" dxfId="5" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="lessThan">
       <formula>5</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="4">
+    <cfRule type="expression" dxfId="1" priority="4">
       <formula>LEN(TRIM(C2))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S27">
-    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>"X"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/matematicas_1ESOA/notas/E1A_evalfinal.xlsx
+++ b/matematicas_1ESOA/notas/E1A_evalfinal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ac4744725179635e/Desktop/sapere_aude/matematicas_1ESOA/notas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="14_{4378DAE7-DBE3-4408-84D4-85DD99A0A7A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85D10536-EA85-4838-91C4-099A8A27A35D}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="14_{0AF2DC00-A680-4ECC-A428-61FD31D5A0AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C39BE5DF-C1E2-409F-B087-B1EDE7213FD3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,8 +36,53 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={8D785663-FF67-4D18-9C52-8B9C2B258453}</author>
+    <author>tc={589B6493-2036-443C-8A79-9679591D5853}</author>
+    <author>tc={3C49B133-989D-4F0B-8DA8-A7335B3718C0}</author>
+    <author>tc={2F1020DE-F48E-4E9D-B52D-DFAEE77BACD8}</author>
+  </authors>
+  <commentList>
+    <comment ref="D9" authorId="0" shapeId="0" xr:uid="{8D785663-FF67-4D18-9C52-8B9C2B258453}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    5 en actilla jefatura</t>
+      </text>
+    </comment>
+    <comment ref="C13" authorId="1" shapeId="0" xr:uid="{589B6493-2036-443C-8A79-9679591D5853}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    comentado por nati por correo</t>
+      </text>
+    </comment>
+    <comment ref="E14" authorId="2" shapeId="0" xr:uid="{3C49B133-989D-4F0B-8DA8-A7335B3718C0}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    5 en actilla jefatura</t>
+      </text>
+    </comment>
+    <comment ref="C18" authorId="3" shapeId="0" xr:uid="{2F1020DE-F48E-4E9D-B52D-DFAEE77BACD8}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    comentado por nati por correo</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="76">
   <si>
     <t>HOJA DE CÁLCULO PARA GENERAR UN ACTILLA DE EVALUACIÓN</t>
   </si>
@@ -357,7 +402,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0\ %"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -433,6 +478,12 @@
       <sz val="12"/>
       <color indexed="8"/>
       <name val="Times New Roman"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -986,7 +1037,9 @@
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Eduardo Olivares López" id="{C977736F-BADA-42D1-BE08-2745CF9B3E52}" userId="ac4744725179635e" providerId="Windows Live"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1284,6 +1337,23 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="D9" dT="2026-06-16T08:35:13.01" personId="{C977736F-BADA-42D1-BE08-2745CF9B3E52}" id="{8D785663-FF67-4D18-9C52-8B9C2B258453}">
+    <text>5 en actilla jefatura</text>
+  </threadedComment>
+  <threadedComment ref="C13" dT="2026-06-16T13:15:00.33" personId="{C977736F-BADA-42D1-BE08-2745CF9B3E52}" id="{589B6493-2036-443C-8A79-9679591D5853}">
+    <text>comentado por nati por correo</text>
+  </threadedComment>
+  <threadedComment ref="E14" dT="2026-06-16T08:36:15.31" personId="{C977736F-BADA-42D1-BE08-2745CF9B3E52}" id="{3C49B133-989D-4F0B-8DA8-A7335B3718C0}">
+    <text>5 en actilla jefatura</text>
+  </threadedComment>
+  <threadedComment ref="C18" dT="2026-06-16T13:14:44.17" personId="{C977736F-BADA-42D1-BE08-2745CF9B3E52}" id="{2F1020DE-F48E-4E9D-B52D-DFAEE77BACD8}">
+    <text>comentado por nati por correo</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:AMK26"/>
@@ -1422,7 +1492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1537,14 +1607,14 @@
       <c r="J2" s="31">
         <v>7</v>
       </c>
-      <c r="K2" s="31" t="s">
-        <v>49</v>
+      <c r="K2" s="31">
+        <v>7</v>
       </c>
       <c r="L2" s="31">
-        <v>4</v>
-      </c>
-      <c r="M2" s="31" t="s">
-        <v>49</v>
+        <v>5</v>
+      </c>
+      <c r="M2" s="31">
+        <v>8</v>
       </c>
       <c r="N2" s="31">
         <v>7</v>
@@ -1560,19 +1630,19 @@
       </c>
       <c r="R2" s="13">
         <f t="shared" ref="R2:R26" si="0">COUNTIF(C2:Q2,"&lt;5")+COUNTIF(C2:Q2,"NP")+COUNTIF(C2:Q2,"NE")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" s="14" t="str">
         <f t="shared" ref="S2:S26" si="1">IF(T2&gt;$T$27,"X","")</f>
-        <v>X</v>
+        <v/>
       </c>
       <c r="T2" s="14">
         <f t="shared" ref="T2:T26" si="2">COUNTBLANK(C2:Q2)</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U2" s="15">
         <f t="shared" ref="U2:U26" si="3">(SUM(C2:Q2)+(COUNTIF(C2:Q2,"10-M")*10))/(COUNTIF(C2:Q2,"10-M")+COUNT(C2:Q2)+COUNTIF(C2:Q2,"NP")+COUNTIF(C2:Q2,"NE"))</f>
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="X2" s="16" t="s">
         <v>22</v>
@@ -1618,8 +1688,8 @@
       <c r="L3" s="31">
         <v>7</v>
       </c>
-      <c r="M3" s="31" t="s">
-        <v>49</v>
+      <c r="M3" s="31">
+        <v>8</v>
       </c>
       <c r="N3" s="31" t="s">
         <v>49</v>
@@ -1643,22 +1713,22 @@
       </c>
       <c r="T3" s="19">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U3" s="20">
         <f t="shared" si="3"/>
-        <v>6.7777777777777777</v>
+        <v>6.9</v>
       </c>
       <c r="W3" s="21">
         <v>0</v>
       </c>
       <c r="X3" s="21">
         <f>COUNTIF(R2:R26,0)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Y3" s="22">
         <f>X3/SUM($X$3:$X$7)</f>
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="4" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
@@ -1698,8 +1768,8 @@
       <c r="L4" s="31">
         <v>7</v>
       </c>
-      <c r="M4" s="31" t="s">
-        <v>49</v>
+      <c r="M4" s="31">
+        <v>9</v>
       </c>
       <c r="N4" s="31" t="s">
         <v>49</v>
@@ -1723,11 +1793,11 @@
       </c>
       <c r="T4" s="14">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U4" s="15">
         <f t="shared" si="3"/>
-        <v>6.2222222222222223</v>
+        <v>6.5</v>
       </c>
       <c r="W4" s="24" t="s">
         <v>24</v>
@@ -1778,8 +1848,8 @@
       <c r="L5" s="31">
         <v>5</v>
       </c>
-      <c r="M5" s="31" t="s">
-        <v>49</v>
+      <c r="M5" s="31">
+        <v>5</v>
       </c>
       <c r="N5" s="31" t="s">
         <v>49</v>
@@ -1803,22 +1873,22 @@
       </c>
       <c r="T5" s="19">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U5" s="20">
         <f t="shared" si="3"/>
-        <v>3.8888888888888888</v>
+        <v>4</v>
       </c>
       <c r="W5" s="24" t="s">
         <v>25</v>
       </c>
       <c r="X5" s="21">
         <f>COUNTIF(R2:R26,"&lt;5")-X3-X4</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y5" s="22">
         <f>X5/SUM($X$3:$X$7)</f>
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="6" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
@@ -1858,8 +1928,8 @@
       <c r="L6" s="31">
         <v>6</v>
       </c>
-      <c r="M6" s="31" t="s">
-        <v>49</v>
+      <c r="M6" s="31">
+        <v>6</v>
       </c>
       <c r="N6" s="31" t="s">
         <v>49</v>
@@ -1883,22 +1953,22 @@
       </c>
       <c r="T6" s="14">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U6" s="15">
         <f t="shared" si="3"/>
-        <v>4.4444444444444446</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="W6" s="24" t="s">
         <v>26</v>
       </c>
       <c r="X6" s="21">
         <f>COUNTIF(R2:R26,"&lt;7")-X3-X4-X5</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6" s="22">
         <f>X6/SUM($X$3:$X$7)</f>
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="7" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
@@ -1938,8 +2008,8 @@
       <c r="L7" s="31">
         <v>9</v>
       </c>
-      <c r="M7" s="31" t="s">
-        <v>49</v>
+      <c r="M7" s="31">
+        <v>9</v>
       </c>
       <c r="N7" s="31">
         <v>8</v>
@@ -1963,22 +2033,22 @@
       </c>
       <c r="T7" s="19">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U7" s="20">
         <f t="shared" si="3"/>
-        <v>8.5555555555555554</v>
+        <v>8.6</v>
       </c>
       <c r="W7" s="24" t="s">
         <v>27</v>
       </c>
       <c r="X7" s="21">
         <f>COUNTIF(R2:R26,"&gt;6")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7" s="22">
         <f>X7/SUM($X$3:$X$7)</f>
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="8" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
@@ -2062,7 +2132,7 @@
         <v>5</v>
       </c>
       <c r="D9" s="31">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E9" s="31">
         <v>5</v>
@@ -2105,7 +2175,7 @@
       </c>
       <c r="R9" s="18">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S9" s="14" t="str">
         <f t="shared" si="1"/>
@@ -2117,7 +2187,7 @@
       </c>
       <c r="U9" s="20">
         <f t="shared" si="3"/>
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="W9" s="32" t="s">
         <v>31</v>
@@ -2162,8 +2232,8 @@
       <c r="L10" s="31">
         <v>9</v>
       </c>
-      <c r="M10" s="31" t="s">
-        <v>49</v>
+      <c r="M10" s="31">
+        <v>9</v>
       </c>
       <c r="N10" s="31" t="s">
         <v>49</v>
@@ -2187,11 +2257,11 @@
       </c>
       <c r="T10" s="14">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U10" s="15">
         <f t="shared" si="3"/>
-        <v>8.3333333333333339</v>
+        <v>8.4</v>
       </c>
       <c r="W10" s="32"/>
       <c r="X10" s="32"/>
@@ -2228,17 +2298,17 @@
       <c r="J11" s="31">
         <v>9</v>
       </c>
-      <c r="K11" s="31" t="s">
-        <v>49</v>
+      <c r="K11" s="31">
+        <v>9</v>
       </c>
       <c r="L11" s="31">
         <v>9</v>
       </c>
-      <c r="M11" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="N11" s="31">
+      <c r="M11" s="31">
         <v>10</v>
+      </c>
+      <c r="N11" s="31" t="s">
+        <v>74</v>
       </c>
       <c r="O11" s="31" t="s">
         <v>49</v>
@@ -2255,15 +2325,15 @@
       </c>
       <c r="S11" s="14" t="str">
         <f t="shared" si="1"/>
-        <v>X</v>
+        <v/>
       </c>
       <c r="T11" s="19">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U11" s="20">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="W11" s="32"/>
       <c r="X11" s="32"/>
@@ -2300,14 +2370,14 @@
       <c r="J12" s="31">
         <v>9</v>
       </c>
-      <c r="K12" s="31" t="s">
-        <v>49</v>
+      <c r="K12" s="31">
+        <v>8</v>
       </c>
       <c r="L12" s="31">
         <v>9</v>
       </c>
-      <c r="M12" s="31" t="s">
-        <v>49</v>
+      <c r="M12" s="31">
+        <v>9</v>
       </c>
       <c r="N12" s="31">
         <v>8</v>
@@ -2327,15 +2397,15 @@
       </c>
       <c r="S12" s="14" t="str">
         <f t="shared" si="1"/>
-        <v>X</v>
+        <v/>
       </c>
       <c r="T12" s="14">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U12" s="15">
         <f t="shared" si="3"/>
-        <v>8.125</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="W12" s="33" t="s">
         <v>75</v>
@@ -2350,8 +2420,8 @@
       <c r="B13" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="31" t="s">
-        <v>49</v>
+      <c r="C13" s="31">
+        <v>4</v>
       </c>
       <c r="D13" s="31">
         <v>3</v>
@@ -2380,8 +2450,8 @@
       <c r="L13" s="31">
         <v>4</v>
       </c>
-      <c r="M13" s="31" t="s">
-        <v>49</v>
+      <c r="M13" s="31">
+        <v>5</v>
       </c>
       <c r="N13" s="31" t="s">
         <v>49</v>
@@ -2397,19 +2467,19 @@
       </c>
       <c r="R13" s="18">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S13" s="14" t="str">
         <f t="shared" si="1"/>
-        <v>X</v>
+        <v/>
       </c>
       <c r="T13" s="19">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U13" s="20">
         <f t="shared" si="3"/>
-        <v>4.125</v>
+        <v>4.2</v>
       </c>
       <c r="W13" s="33"/>
       <c r="X13" s="33"/>
@@ -2452,8 +2522,8 @@
       <c r="L14" s="31">
         <v>7</v>
       </c>
-      <c r="M14" s="31" t="s">
-        <v>49</v>
+      <c r="M14" s="31">
+        <v>8</v>
       </c>
       <c r="N14" s="31" t="s">
         <v>49</v>
@@ -2477,11 +2547,11 @@
       </c>
       <c r="T14" s="14">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U14" s="15">
         <f t="shared" si="3"/>
-        <v>5.666666666666667</v>
+        <v>5.9</v>
       </c>
       <c r="W14" s="33"/>
       <c r="X14" s="33"/>
@@ -2518,14 +2588,14 @@
       <c r="J15" s="31">
         <v>6</v>
       </c>
-      <c r="K15" s="31" t="s">
-        <v>49</v>
+      <c r="K15" s="31">
+        <v>5</v>
       </c>
       <c r="L15" s="31">
         <v>7</v>
       </c>
-      <c r="M15" s="31" t="s">
-        <v>49</v>
+      <c r="M15" s="31">
+        <v>8</v>
       </c>
       <c r="N15" s="31">
         <v>6</v>
@@ -2545,15 +2615,15 @@
       </c>
       <c r="S15" s="14" t="str">
         <f t="shared" si="1"/>
-        <v>X</v>
+        <v/>
       </c>
       <c r="T15" s="19">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U15" s="20">
         <f t="shared" si="3"/>
-        <v>6.25</v>
+        <v>6.3</v>
       </c>
       <c r="W15" s="34" t="s">
         <v>30</v>
@@ -2598,8 +2668,8 @@
       <c r="L16" s="31">
         <v>6</v>
       </c>
-      <c r="M16" s="31" t="s">
-        <v>49</v>
+      <c r="M16" s="31">
+        <v>7</v>
       </c>
       <c r="N16" s="31" t="s">
         <v>49</v>
@@ -2623,11 +2693,11 @@
       </c>
       <c r="T16" s="14">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U16" s="15">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="17" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
@@ -2706,8 +2776,8 @@
       <c r="B18" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="C18" s="31" t="s">
-        <v>49</v>
+      <c r="C18" s="31">
+        <v>4</v>
       </c>
       <c r="D18" s="31">
         <v>3</v>
@@ -2753,7 +2823,7 @@
       </c>
       <c r="R18" s="13">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S18" s="14" t="str">
         <f t="shared" si="1"/>
@@ -2761,11 +2831,11 @@
       </c>
       <c r="T18" s="14">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U18" s="15">
         <f t="shared" si="3"/>
-        <v>5.5555555555555554</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="19" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
@@ -2799,8 +2869,8 @@
       <c r="J19" s="31">
         <v>9</v>
       </c>
-      <c r="K19" s="31" t="s">
-        <v>49</v>
+      <c r="K19" s="31">
+        <v>7</v>
       </c>
       <c r="L19" s="31">
         <v>8</v>
@@ -2830,11 +2900,11 @@
       </c>
       <c r="T19" s="19">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U19" s="20">
         <f t="shared" si="3"/>
-        <v>8.1111111111111107</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
@@ -2874,8 +2944,8 @@
       <c r="L20" s="31">
         <v>5</v>
       </c>
-      <c r="M20" s="31" t="s">
-        <v>49</v>
+      <c r="M20" s="31">
+        <v>7</v>
       </c>
       <c r="N20" s="31" t="s">
         <v>49</v>
@@ -2899,11 +2969,11 @@
       </c>
       <c r="T20" s="14">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U20" s="15">
         <f t="shared" si="3"/>
-        <v>5.8888888888888893</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
@@ -2937,8 +3007,8 @@
       <c r="J21" s="31">
         <v>8</v>
       </c>
-      <c r="K21" s="31" t="s">
-        <v>49</v>
+      <c r="K21" s="31">
+        <v>7</v>
       </c>
       <c r="L21" s="31">
         <v>7</v>
@@ -2968,11 +3038,11 @@
       </c>
       <c r="T21" s="19">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U21" s="20">
         <f t="shared" si="3"/>
-        <v>7.666666666666667</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="22" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
@@ -3006,14 +3076,14 @@
       <c r="J22" s="31">
         <v>9</v>
       </c>
-      <c r="K22" s="31" t="s">
-        <v>49</v>
+      <c r="K22" s="31">
+        <v>7</v>
       </c>
       <c r="L22" s="31">
         <v>9</v>
       </c>
-      <c r="M22" s="31" t="s">
-        <v>49</v>
+      <c r="M22" s="31">
+        <v>10</v>
       </c>
       <c r="N22" s="31">
         <v>10</v>
@@ -3033,15 +3103,15 @@
       </c>
       <c r="S22" s="14" t="str">
         <f t="shared" si="1"/>
-        <v>X</v>
+        <v/>
       </c>
       <c r="T22" s="14">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U22" s="15">
         <f t="shared" si="3"/>
-        <v>8.375</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="23" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
@@ -3148,10 +3218,10 @@
         <v>49</v>
       </c>
       <c r="L24" s="31">
-        <v>4</v>
-      </c>
-      <c r="M24" s="31" t="s">
-        <v>49</v>
+        <v>5</v>
+      </c>
+      <c r="M24" s="31">
+        <v>5</v>
       </c>
       <c r="N24" s="31" t="s">
         <v>49</v>
@@ -3167,7 +3237,7 @@
       </c>
       <c r="R24" s="13">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S24" s="14" t="str">
         <f t="shared" si="1"/>
@@ -3175,11 +3245,11 @@
       </c>
       <c r="T24" s="14">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U24" s="15">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>5.0999999999999996</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
@@ -3219,8 +3289,8 @@
       <c r="L25" s="31">
         <v>7</v>
       </c>
-      <c r="M25" s="31" t="s">
-        <v>49</v>
+      <c r="M25" s="31">
+        <v>9</v>
       </c>
       <c r="N25" s="31" t="s">
         <v>49</v>
@@ -3244,11 +3314,11 @@
       </c>
       <c r="T25" s="19">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U25" s="20">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="26" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
@@ -3282,14 +3352,14 @@
       <c r="J26" s="31">
         <v>8</v>
       </c>
-      <c r="K26" s="31" t="s">
-        <v>49</v>
+      <c r="K26" s="31">
+        <v>9</v>
       </c>
       <c r="L26" s="31">
         <v>9</v>
       </c>
-      <c r="M26" s="31" t="s">
-        <v>49</v>
+      <c r="M26" s="31">
+        <v>9</v>
       </c>
       <c r="N26" s="31">
         <v>10</v>
@@ -3309,15 +3379,15 @@
       </c>
       <c r="S26" s="14" t="str">
         <f t="shared" si="1"/>
-        <v>X</v>
+        <v/>
       </c>
       <c r="T26" s="14">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U26" s="15">
         <f t="shared" si="3"/>
-        <v>8.75</v>
+        <v>8.8000000000000007</v>
       </c>
     </row>
     <row r="27" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
@@ -3326,11 +3396,11 @@
       </c>
       <c r="C27" s="26">
         <f t="shared" ref="C27:Q27" si="4">COUNTIF(C2:C26,"&lt;5")</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D27" s="26">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E27" s="26">
         <f t="shared" si="4"/>
@@ -3362,7 +3432,7 @@
       </c>
       <c r="L27" s="26">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M27" s="26">
         <f t="shared" si="4"/>
@@ -3386,7 +3456,7 @@
       </c>
       <c r="R27" s="27">
         <f>AVERAGE(R2:R26)</f>
-        <v>1.2</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="S27" s="14" t="str">
         <f>IF(T27&lt;$T$27,"X","")</f>
@@ -3394,11 +3464,11 @@
       </c>
       <c r="T27" s="28">
         <f>MODE(T2:T26)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U27" s="15">
         <f>(SUM(C2:Q26)+(COUNTIF(C2:Q26,"10-M")*10))/(COUNTIF(C2:Q26,"10-M")+COUNT(C2:Q26)+COUNTIF(C2:Q26,"NP")+COUNTIF(C2:Q26,"NE"))</f>
-        <v>6.5990990990990994</v>
+        <v>6.7039999999999997</v>
       </c>
     </row>
     <row r="28" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
@@ -3407,11 +3477,11 @@
       </c>
       <c r="C28" s="29">
         <f t="shared" ref="C28:Q28" si="5">IF((COUNT(C2:C26)+COUNTIF(C2:C26,"10-M"))=0,"--",C27/(COUNT(C2:C26)+COUNTIF(C2:C26,"10-M")))</f>
-        <v>8.6956521739130432E-2</v>
+        <v>0.16</v>
       </c>
       <c r="D28" s="29">
         <f t="shared" si="5"/>
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="E28" s="29">
         <f t="shared" si="5"/>
@@ -3437,13 +3507,13 @@
         <f t="shared" si="5"/>
         <v>0.2</v>
       </c>
-      <c r="K28" s="29" t="str">
+      <c r="K28" s="29">
         <f t="shared" si="5"/>
-        <v>--</v>
+        <v>0</v>
       </c>
       <c r="L28" s="29">
         <f t="shared" si="5"/>
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="M28" s="29">
         <f t="shared" si="5"/>
@@ -3501,5 +3571,6 @@
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/matematicas_1ESOA/notas/E1A_evalfinal.xlsx
+++ b/matematicas_1ESOA/notas/E1A_evalfinal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ac4744725179635e/Desktop/sapere_aude/matematicas_1ESOA/notas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="14_{0AF2DC00-A680-4ECC-A428-61FD31D5A0AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C39BE5DF-C1E2-409F-B087-B1EDE7213FD3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{5F37CBA6-FC45-411C-9E35-2F8522B360D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="76">
   <si>
     <t>HOJA DE CÁLCULO PARA GENERAR UN ACTILLA DE EVALUACIÓN</t>
   </si>
@@ -402,7 +402,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0\ %"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -478,12 +478,6 @@
       <sz val="12"/>
       <color indexed="8"/>
       <name val="Times New Roman"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
